--- a/output/version3/test/10-5/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C2" t="n">
-        <v>587</v>
+        <v>467</v>
       </c>
       <c r="D2" t="n">
-        <v>523</v>
+        <v>427</v>
       </c>
       <c r="E2" t="n">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="F2" t="n">
-        <v>484</v>
+        <v>436</v>
       </c>
       <c r="G2" t="n">
-        <v>545</v>
+        <v>443</v>
       </c>
       <c r="H2" t="n">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="I2" t="n">
-        <v>549</v>
+        <v>443</v>
       </c>
       <c r="J2" t="n">
-        <v>545</v>
+        <v>475</v>
       </c>
       <c r="K2" t="n">
-        <v>526</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>522</v>
+        <v>452.2</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C3" t="n">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="D3" t="n">
-        <v>558</v>
+        <v>477</v>
       </c>
       <c r="E3" t="n">
-        <v>588</v>
+        <v>488</v>
       </c>
       <c r="F3" t="n">
-        <v>548</v>
+        <v>508</v>
       </c>
       <c r="G3" t="n">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="H3" t="n">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="I3" t="n">
-        <v>515</v>
+        <v>463</v>
       </c>
       <c r="J3" t="n">
-        <v>539</v>
+        <v>432</v>
       </c>
       <c r="K3" t="n">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="L3" t="n">
-        <v>524.6</v>
+        <v>482.3</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>634</v>
+        <v>503</v>
       </c>
       <c r="C4" t="n">
-        <v>571</v>
+        <v>503</v>
       </c>
       <c r="D4" t="n">
-        <v>543</v>
+        <v>482</v>
       </c>
       <c r="E4" t="n">
-        <v>581</v>
+        <v>503</v>
       </c>
       <c r="F4" t="n">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G4" t="n">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="H4" t="n">
-        <v>565</v>
+        <v>497</v>
       </c>
       <c r="I4" t="n">
-        <v>531</v>
+        <v>586</v>
       </c>
       <c r="J4" t="n">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="K4" t="n">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="L4" t="n">
-        <v>551.9</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C5" t="n">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D5" t="n">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="E5" t="n">
-        <v>521</v>
+        <v>452</v>
       </c>
       <c r="F5" t="n">
-        <v>456</v>
+        <v>507</v>
       </c>
       <c r="G5" t="n">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="H5" t="n">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="I5" t="n">
-        <v>478</v>
+        <v>507</v>
       </c>
       <c r="J5" t="n">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>490.7</v>
+        <v>490.3</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>557</v>
+        <v>518</v>
       </c>
       <c r="D6" t="n">
-        <v>574</v>
+        <v>424</v>
       </c>
       <c r="E6" t="n">
-        <v>547</v>
+        <v>444</v>
       </c>
       <c r="F6" t="n">
+        <v>440</v>
+      </c>
+      <c r="G6" t="n">
+        <v>444</v>
+      </c>
+      <c r="H6" t="n">
         <v>474</v>
       </c>
-      <c r="G6" t="n">
-        <v>563</v>
-      </c>
-      <c r="H6" t="n">
-        <v>520</v>
-      </c>
       <c r="I6" t="n">
-        <v>509</v>
+        <v>440</v>
       </c>
       <c r="J6" t="n">
-        <v>552</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>537</v>
+        <v>494</v>
       </c>
       <c r="L6" t="n">
-        <v>536.6</v>
+        <v>454.7</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>526</v>
+        <v>483</v>
       </c>
       <c r="C7" t="n">
-        <v>550</v>
+        <v>483</v>
       </c>
       <c r="D7" t="n">
+        <v>461</v>
+      </c>
+      <c r="E7" t="n">
+        <v>461</v>
+      </c>
+      <c r="F7" t="n">
         <v>503</v>
       </c>
-      <c r="E7" t="n">
-        <v>504</v>
-      </c>
-      <c r="F7" t="n">
-        <v>501</v>
-      </c>
       <c r="G7" t="n">
-        <v>570</v>
+        <v>461</v>
       </c>
       <c r="H7" t="n">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="I7" t="n">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="J7" t="n">
-        <v>533</v>
+        <v>471</v>
       </c>
       <c r="K7" t="n">
-        <v>505</v>
+        <v>447</v>
       </c>
       <c r="L7" t="n">
-        <v>508.7</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="C8" t="n">
-        <v>524</v>
+        <v>452</v>
       </c>
       <c r="D8" t="n">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="E8" t="n">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="F8" t="n">
-        <v>553</v>
+        <v>478</v>
       </c>
       <c r="G8" t="n">
-        <v>561</v>
+        <v>523</v>
       </c>
       <c r="H8" t="n">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="I8" t="n">
-        <v>535</v>
+        <v>491</v>
       </c>
       <c r="J8" t="n">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="K8" t="n">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="L8" t="n">
-        <v>547.7</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>435</v>
       </c>
       <c r="D9" t="n">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="E9" t="n">
-        <v>555</v>
+        <v>448</v>
       </c>
       <c r="F9" t="n">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="G9" t="n">
-        <v>422</v>
+        <v>489</v>
       </c>
       <c r="H9" t="n">
-        <v>492</v>
+        <v>461</v>
       </c>
       <c r="I9" t="n">
-        <v>486</v>
+        <v>448</v>
       </c>
       <c r="J9" t="n">
-        <v>521</v>
+        <v>436</v>
       </c>
       <c r="K9" t="n">
-        <v>492</v>
+        <v>383</v>
       </c>
       <c r="L9" t="n">
-        <v>499.2</v>
+        <v>456.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>541</v>
+        <v>492</v>
       </c>
       <c r="C10" t="n">
-        <v>587</v>
+        <v>475</v>
       </c>
       <c r="D10" t="n">
-        <v>533</v>
+        <v>488</v>
       </c>
       <c r="E10" t="n">
-        <v>529</v>
+        <v>446</v>
       </c>
       <c r="F10" t="n">
-        <v>564</v>
+        <v>439</v>
       </c>
       <c r="G10" t="n">
-        <v>512</v>
+        <v>491</v>
       </c>
       <c r="H10" t="n">
-        <v>609</v>
+        <v>491</v>
       </c>
       <c r="I10" t="n">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="J10" t="n">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="K10" t="n">
-        <v>555</v>
+        <v>494</v>
       </c>
       <c r="L10" t="n">
-        <v>543.6</v>
+        <v>477.2</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>522</v>
+        <v>453</v>
       </c>
       <c r="C11" t="n">
-        <v>500</v>
+        <v>457</v>
       </c>
       <c r="D11" t="n">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="E11" t="n">
-        <v>494</v>
+        <v>431</v>
       </c>
       <c r="F11" t="n">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="G11" t="n">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="H11" t="n">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="I11" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="J11" t="n">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="K11" t="n">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="L11" t="n">
-        <v>488.2</v>
+        <v>452.8</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>604</v>
+        <v>509</v>
       </c>
       <c r="C12" t="n">
-        <v>574</v>
+        <v>499</v>
       </c>
       <c r="D12" t="n">
-        <v>590</v>
+        <v>541</v>
       </c>
       <c r="E12" t="n">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="F12" t="n">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="G12" t="n">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="H12" t="n">
-        <v>638</v>
+        <v>541</v>
       </c>
       <c r="I12" t="n">
-        <v>533</v>
+        <v>476</v>
       </c>
       <c r="J12" t="n">
-        <v>583</v>
+        <v>539</v>
       </c>
       <c r="K12" t="n">
-        <v>629</v>
+        <v>510</v>
       </c>
       <c r="L12" t="n">
-        <v>575.4</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="C13" t="n">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="D13" t="n">
-        <v>573</v>
+        <v>533</v>
       </c>
       <c r="E13" t="n">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="F13" t="n">
-        <v>436</v>
+        <v>556</v>
       </c>
       <c r="G13" t="n">
-        <v>509</v>
+        <v>532</v>
       </c>
       <c r="H13" t="n">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="I13" t="n">
-        <v>580</v>
+        <v>501</v>
       </c>
       <c r="J13" t="n">
-        <v>524</v>
+        <v>497</v>
       </c>
       <c r="K13" t="n">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="L13" t="n">
-        <v>521.7</v>
+        <v>530.6</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>507</v>
+        <v>568</v>
       </c>
       <c r="C14" t="n">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="D14" t="n">
-        <v>613</v>
+        <v>511</v>
       </c>
       <c r="E14" t="n">
-        <v>547</v>
+        <v>486</v>
       </c>
       <c r="F14" t="n">
-        <v>577</v>
+        <v>550</v>
       </c>
       <c r="G14" t="n">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="H14" t="n">
-        <v>586</v>
+        <v>516</v>
       </c>
       <c r="I14" t="n">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="J14" t="n">
-        <v>649</v>
+        <v>539</v>
       </c>
       <c r="K14" t="n">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="L14" t="n">
-        <v>560.9</v>
+        <v>533.5</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>532</v>
+        <v>469</v>
       </c>
       <c r="C15" t="n">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="D15" t="n">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="E15" t="n">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="F15" t="n">
-        <v>554</v>
+        <v>484</v>
       </c>
       <c r="G15" t="n">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="H15" t="n">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="I15" t="n">
-        <v>556</v>
+        <v>444</v>
       </c>
       <c r="J15" t="n">
-        <v>600</v>
+        <v>499</v>
       </c>
       <c r="K15" t="n">
-        <v>561</v>
+        <v>456</v>
       </c>
       <c r="L15" t="n">
-        <v>520.2</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>554</v>
+        <v>514</v>
       </c>
       <c r="C16" t="n">
-        <v>558</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>568</v>
+        <v>447</v>
       </c>
       <c r="E16" t="n">
-        <v>541</v>
+        <v>496</v>
       </c>
       <c r="F16" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="G16" t="n">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="H16" t="n">
-        <v>542</v>
+        <v>458</v>
       </c>
       <c r="I16" t="n">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="J16" t="n">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="K16" t="n">
-        <v>580</v>
+        <v>424</v>
       </c>
       <c r="L16" t="n">
-        <v>530.3</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="C17" t="n">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="D17" t="n">
-        <v>578</v>
+        <v>489</v>
       </c>
       <c r="E17" t="n">
-        <v>550</v>
+        <v>468</v>
       </c>
       <c r="F17" t="n">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="G17" t="n">
-        <v>556</v>
+        <v>431</v>
       </c>
       <c r="H17" t="n">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="I17" t="n">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="J17" t="n">
-        <v>516</v>
+        <v>456</v>
       </c>
       <c r="K17" t="n">
-        <v>526</v>
+        <v>441</v>
       </c>
       <c r="L17" t="n">
-        <v>514.6</v>
+        <v>463.3</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>608</v>
+        <v>516</v>
       </c>
       <c r="C18" t="n">
-        <v>677</v>
+        <v>514</v>
       </c>
       <c r="D18" t="n">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="E18" t="n">
-        <v>537</v>
+        <v>484</v>
       </c>
       <c r="F18" t="n">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G18" t="n">
-        <v>626</v>
+        <v>476</v>
       </c>
       <c r="H18" t="n">
-        <v>597</v>
+        <v>551</v>
       </c>
       <c r="I18" t="n">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="J18" t="n">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="K18" t="n">
-        <v>598</v>
+        <v>487</v>
       </c>
       <c r="L18" t="n">
-        <v>586.7</v>
+        <v>517.2</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>496</v>
+        <v>547</v>
       </c>
       <c r="C19" t="n">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="D19" t="n">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="E19" t="n">
-        <v>496</v>
+        <v>595</v>
       </c>
       <c r="F19" t="n">
-        <v>557</v>
+        <v>510</v>
       </c>
       <c r="G19" t="n">
-        <v>538</v>
+        <v>489</v>
       </c>
       <c r="H19" t="n">
-        <v>502</v>
+        <v>548</v>
       </c>
       <c r="I19" t="n">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="J19" t="n">
-        <v>582</v>
+        <v>536</v>
       </c>
       <c r="K19" t="n">
-        <v>496</v>
+        <v>536</v>
       </c>
       <c r="L19" t="n">
-        <v>526.4</v>
+        <v>534.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>613</v>
+        <v>484</v>
       </c>
       <c r="C20" t="n">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="D20" t="n">
-        <v>450</v>
+        <v>522</v>
       </c>
       <c r="E20" t="n">
-        <v>560</v>
+        <v>455</v>
       </c>
       <c r="F20" t="n">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="G20" t="n">
-        <v>601</v>
+        <v>496</v>
       </c>
       <c r="H20" t="n">
-        <v>533</v>
+        <v>465</v>
       </c>
       <c r="I20" t="n">
-        <v>575</v>
+        <v>457</v>
       </c>
       <c r="J20" t="n">
-        <v>540</v>
+        <v>476</v>
       </c>
       <c r="K20" t="n">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="L20" t="n">
-        <v>530.9</v>
+        <v>481.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C21" t="n">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="D21" t="n">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="E21" t="n">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="F21" t="n">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G21" t="n">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="H21" t="n">
-        <v>506</v>
+        <v>425</v>
       </c>
       <c r="I21" t="n">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="J21" t="n">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="K21" t="n">
-        <v>522</v>
+        <v>464</v>
       </c>
       <c r="L21" t="n">
-        <v>476.9</v>
+        <v>462.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C22" t="n">
-        <v>532</v>
+        <v>482</v>
       </c>
       <c r="D22" t="n">
-        <v>513</v>
+        <v>566</v>
       </c>
       <c r="E22" t="n">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="F22" t="n">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="G22" t="n">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="H22" t="n">
-        <v>428</v>
+        <v>482</v>
       </c>
       <c r="I22" t="n">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="J22" t="n">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="K22" t="n">
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="L22" t="n">
-        <v>479.3</v>
+        <v>497.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>410</v>
+        <v>477</v>
       </c>
       <c r="C23" t="n">
-        <v>387</v>
+        <v>448</v>
       </c>
       <c r="D23" t="n">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="E23" t="n">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="F23" t="n">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="G23" t="n">
-        <v>435</v>
+        <v>484</v>
       </c>
       <c r="H23" t="n">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="I23" t="n">
-        <v>550</v>
+        <v>484</v>
       </c>
       <c r="J23" t="n">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="K23" t="n">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="L23" t="n">
-        <v>444.1</v>
+        <v>464.6</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>477</v>
+        <v>426</v>
       </c>
       <c r="C24" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="D24" t="n">
-        <v>487</v>
+        <v>406</v>
       </c>
       <c r="E24" t="n">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="F24" t="n">
-        <v>571</v>
+        <v>419</v>
       </c>
       <c r="G24" t="n">
-        <v>481</v>
+        <v>393</v>
       </c>
       <c r="H24" t="n">
-        <v>477</v>
+        <v>421</v>
       </c>
       <c r="I24" t="n">
-        <v>524</v>
+        <v>430</v>
       </c>
       <c r="J24" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="K24" t="n">
-        <v>540</v>
+        <v>438</v>
       </c>
       <c r="L24" t="n">
-        <v>491.6</v>
+        <v>424.8</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C25" t="n">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="D25" t="n">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="E25" t="n">
-        <v>527</v>
+        <v>418</v>
       </c>
       <c r="F25" t="n">
-        <v>462</v>
+        <v>421</v>
       </c>
       <c r="G25" t="n">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="H25" t="n">
+        <v>392</v>
+      </c>
+      <c r="I25" t="n">
+        <v>422</v>
+      </c>
+      <c r="J25" t="n">
+        <v>447</v>
+      </c>
+      <c r="K25" t="n">
         <v>425</v>
       </c>
-      <c r="I25" t="n">
-        <v>417</v>
-      </c>
-      <c r="J25" t="n">
-        <v>498</v>
-      </c>
-      <c r="K25" t="n">
-        <v>494</v>
-      </c>
       <c r="L25" t="n">
-        <v>454.5</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="C26" t="n">
-        <v>534</v>
+        <v>650</v>
       </c>
       <c r="D26" t="n">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="E26" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F26" t="n">
-        <v>637</v>
+        <v>540</v>
       </c>
       <c r="G26" t="n">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="H26" t="n">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="I26" t="n">
-        <v>554</v>
+        <v>622</v>
       </c>
       <c r="J26" t="n">
-        <v>600</v>
+        <v>564</v>
       </c>
       <c r="K26" t="n">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="L26" t="n">
-        <v>567</v>
+        <v>575.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="C27" t="n">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="D27" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="E27" t="n">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="F27" t="n">
-        <v>507</v>
+        <v>466</v>
       </c>
       <c r="G27" t="n">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="H27" t="n">
-        <v>543</v>
+        <v>429</v>
       </c>
       <c r="I27" t="n">
-        <v>546</v>
+        <v>439</v>
       </c>
       <c r="J27" t="n">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="K27" t="n">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="L27" t="n">
-        <v>477.1</v>
+        <v>436.6</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>502</v>
+        <v>436</v>
       </c>
       <c r="C28" t="n">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="D28" t="n">
-        <v>489</v>
+        <v>440</v>
       </c>
       <c r="E28" t="n">
+        <v>432</v>
+      </c>
+      <c r="F28" t="n">
+        <v>436</v>
+      </c>
+      <c r="G28" t="n">
+        <v>440</v>
+      </c>
+      <c r="H28" t="n">
+        <v>440</v>
+      </c>
+      <c r="I28" t="n">
+        <v>501</v>
+      </c>
+      <c r="J28" t="n">
         <v>474</v>
       </c>
-      <c r="F28" t="n">
-        <v>526</v>
-      </c>
-      <c r="G28" t="n">
-        <v>539</v>
-      </c>
-      <c r="H28" t="n">
-        <v>491</v>
-      </c>
-      <c r="I28" t="n">
-        <v>512</v>
-      </c>
-      <c r="J28" t="n">
-        <v>525</v>
-      </c>
       <c r="K28" t="n">
-        <v>478</v>
+        <v>440</v>
       </c>
       <c r="L28" t="n">
-        <v>500.2</v>
+        <v>447.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C29" t="n">
-        <v>502</v>
+        <v>456</v>
       </c>
       <c r="D29" t="n">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="E29" t="n">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="F29" t="n">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="G29" t="n">
-        <v>491</v>
+        <v>460</v>
       </c>
       <c r="H29" t="n">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="I29" t="n">
-        <v>507</v>
+        <v>433</v>
       </c>
       <c r="J29" t="n">
-        <v>463</v>
+        <v>418</v>
       </c>
       <c r="K29" t="n">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="L29" t="n">
-        <v>480.7</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="C30" t="n">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="D30" t="n">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="E30" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
       <c r="F30" t="n">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="G30" t="n">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="H30" t="n">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="I30" t="n">
-        <v>531</v>
+        <v>470</v>
       </c>
       <c r="J30" t="n">
-        <v>528</v>
+        <v>473</v>
       </c>
       <c r="K30" t="n">
-        <v>569</v>
+        <v>394</v>
       </c>
       <c r="L30" t="n">
-        <v>475.2</v>
+        <v>458.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>528</v>
+        <v>432</v>
       </c>
       <c r="C31" t="n">
-        <v>606</v>
+        <v>392</v>
       </c>
       <c r="D31" t="n">
-        <v>546</v>
+        <v>472</v>
       </c>
       <c r="E31" t="n">
-        <v>503</v>
+        <v>467</v>
       </c>
       <c r="F31" t="n">
-        <v>498</v>
+        <v>457</v>
       </c>
       <c r="G31" t="n">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="H31" t="n">
-        <v>584</v>
+        <v>491</v>
       </c>
       <c r="I31" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J31" t="n">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="K31" t="n">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="L31" t="n">
-        <v>521.5</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="C32" t="n">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="D32" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E32" t="n">
-        <v>528</v>
+        <v>438</v>
       </c>
       <c r="F32" t="n">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="G32" t="n">
-        <v>574</v>
+        <v>455</v>
       </c>
       <c r="H32" t="n">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="I32" t="n">
-        <v>461</v>
+        <v>405</v>
       </c>
       <c r="J32" t="n">
-        <v>456</v>
+        <v>420</v>
       </c>
       <c r="K32" t="n">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="L32" t="n">
-        <v>470.5</v>
+        <v>436.6</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>358</v>
+        <v>408</v>
       </c>
       <c r="C33" t="n">
-        <v>496</v>
+        <v>450</v>
       </c>
       <c r="D33" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E33" t="n">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="F33" t="n">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="G33" t="n">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="H33" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="I33" t="n">
-        <v>545</v>
+        <v>423</v>
       </c>
       <c r="J33" t="n">
-        <v>485</v>
+        <v>383</v>
       </c>
       <c r="K33" t="n">
-        <v>529</v>
+        <v>388</v>
       </c>
       <c r="L33" t="n">
-        <v>474.5</v>
+        <v>414.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>522</v>
+        <v>415</v>
       </c>
       <c r="C34" t="n">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="D34" t="n">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="E34" t="n">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F34" t="n">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="G34" t="n">
-        <v>504</v>
+        <v>440</v>
       </c>
       <c r="H34" t="n">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="I34" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J34" t="n">
-        <v>500</v>
+        <v>457</v>
       </c>
       <c r="K34" t="n">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="L34" t="n">
-        <v>470.6</v>
+        <v>440.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>574</v>
+        <v>541</v>
       </c>
       <c r="C35" t="n">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="D35" t="n">
-        <v>456</v>
+        <v>552</v>
       </c>
       <c r="E35" t="n">
-        <v>570</v>
+        <v>525</v>
       </c>
       <c r="F35" t="n">
-        <v>469</v>
+        <v>514</v>
       </c>
       <c r="G35" t="n">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="H35" t="n">
-        <v>482</v>
+        <v>553</v>
       </c>
       <c r="I35" t="n">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="J35" t="n">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="K35" t="n">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L35" t="n">
-        <v>510.6</v>
+        <v>525.7</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>478</v>
+        <v>376</v>
       </c>
       <c r="C36" t="n">
-        <v>439</v>
+        <v>380</v>
       </c>
       <c r="D36" t="n">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="E36" t="n">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F36" t="n">
-        <v>446</v>
+        <v>387</v>
       </c>
       <c r="G36" t="n">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="H36" t="n">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="I36" t="n">
-        <v>385</v>
+        <v>447</v>
       </c>
       <c r="J36" t="n">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="K36" t="n">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="L36" t="n">
-        <v>433.7</v>
+        <v>410.9</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C37" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D37" t="n">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="E37" t="n">
-        <v>504</v>
+        <v>426</v>
       </c>
       <c r="F37" t="n">
-        <v>496</v>
+        <v>447</v>
       </c>
       <c r="G37" t="n">
-        <v>432</v>
+        <v>494</v>
       </c>
       <c r="H37" t="n">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="I37" t="n">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="J37" t="n">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="K37" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="L37" t="n">
-        <v>471.7</v>
+        <v>451.8</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="C38" t="n">
-        <v>805</v>
+        <v>512</v>
       </c>
       <c r="D38" t="n">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="E38" t="n">
-        <v>662</v>
+        <v>544</v>
       </c>
       <c r="F38" t="n">
-        <v>627</v>
+        <v>546</v>
       </c>
       <c r="G38" t="n">
-        <v>558</v>
+        <v>500</v>
       </c>
       <c r="H38" t="n">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="I38" t="n">
-        <v>645</v>
+        <v>524</v>
       </c>
       <c r="J38" t="n">
-        <v>664</v>
+        <v>542</v>
       </c>
       <c r="K38" t="n">
-        <v>602</v>
+        <v>557</v>
       </c>
       <c r="L38" t="n">
-        <v>636</v>
+        <v>544.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
+        <v>442</v>
+      </c>
+      <c r="C39" t="n">
+        <v>446</v>
+      </c>
+      <c r="D39" t="n">
         <v>438</v>
       </c>
-      <c r="C39" t="n">
-        <v>403</v>
-      </c>
-      <c r="D39" t="n">
-        <v>466</v>
-      </c>
       <c r="E39" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F39" t="n">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="G39" t="n">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="H39" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I39" t="n">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="J39" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K39" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L39" t="n">
-        <v>411.9</v>
+        <v>411.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="C40" t="n">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="D40" t="n">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="E40" t="n">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="F40" t="n">
+        <v>494</v>
+      </c>
+      <c r="G40" t="n">
         <v>482</v>
       </c>
-      <c r="G40" t="n">
-        <v>481</v>
-      </c>
       <c r="H40" t="n">
-        <v>499</v>
+        <v>534</v>
       </c>
       <c r="I40" t="n">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="J40" t="n">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="K40" t="n">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="L40" t="n">
-        <v>490.2</v>
+        <v>480.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="C41" t="n">
-        <v>469</v>
+        <v>575</v>
       </c>
       <c r="D41" t="n">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="E41" t="n">
-        <v>496</v>
+        <v>536</v>
       </c>
       <c r="F41" t="n">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="G41" t="n">
-        <v>486</v>
+        <v>547</v>
       </c>
       <c r="H41" t="n">
-        <v>627</v>
+        <v>524</v>
       </c>
       <c r="I41" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="J41" t="n">
-        <v>620</v>
+        <v>512</v>
       </c>
       <c r="K41" t="n">
         <v>487</v>
       </c>
       <c r="L41" t="n">
-        <v>524.3</v>
+        <v>535.3</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>413</v>
+        <v>485</v>
       </c>
       <c r="C42" t="n">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D42" t="n">
-        <v>498</v>
+        <v>439</v>
       </c>
       <c r="E42" t="n">
-        <v>568</v>
+        <v>437</v>
       </c>
       <c r="F42" t="n">
-        <v>547</v>
+        <v>508</v>
       </c>
       <c r="G42" t="n">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="H42" t="n">
-        <v>527</v>
+        <v>453</v>
       </c>
       <c r="I42" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="J42" t="n">
-        <v>531</v>
+        <v>480</v>
       </c>
       <c r="K42" t="n">
-        <v>502</v>
+        <v>438</v>
       </c>
       <c r="L42" t="n">
-        <v>495.2</v>
+        <v>457</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="C43" t="n">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="D43" t="n">
-        <v>535</v>
+        <v>505</v>
       </c>
       <c r="E43" t="n">
-        <v>402</v>
+        <v>489</v>
       </c>
       <c r="F43" t="n">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="G43" t="n">
-        <v>495</v>
+        <v>442</v>
       </c>
       <c r="H43" t="n">
-        <v>504</v>
+        <v>444</v>
       </c>
       <c r="I43" t="n">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="J43" t="n">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="K43" t="n">
-        <v>534</v>
+        <v>487</v>
       </c>
       <c r="L43" t="n">
-        <v>498</v>
+        <v>474.2</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>433</v>
+        <v>500</v>
       </c>
       <c r="C44" t="n">
-        <v>562</v>
+        <v>408</v>
       </c>
       <c r="D44" t="n">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="E44" t="n">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="F44" t="n">
         <v>460</v>
       </c>
       <c r="G44" t="n">
-        <v>585</v>
+        <v>461</v>
       </c>
       <c r="H44" t="n">
-        <v>529</v>
+        <v>466</v>
       </c>
       <c r="I44" t="n">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="J44" t="n">
-        <v>404</v>
+        <v>460</v>
       </c>
       <c r="K44" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L44" t="n">
-        <v>483.1</v>
+        <v>454.5</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C45" t="n">
-        <v>512</v>
+        <v>478</v>
       </c>
       <c r="D45" t="n">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="E45" t="n">
-        <v>552</v>
+        <v>462</v>
       </c>
       <c r="F45" t="n">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="G45" t="n">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="H45" t="n">
-        <v>539</v>
+        <v>447</v>
       </c>
       <c r="I45" t="n">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="J45" t="n">
-        <v>507</v>
+        <v>466</v>
       </c>
       <c r="K45" t="n">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="L45" t="n">
-        <v>516.4</v>
+        <v>480.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>436</v>
+        <v>373</v>
       </c>
       <c r="C46" t="n">
-        <v>424</v>
+        <v>389</v>
       </c>
       <c r="D46" t="n">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="E46" t="n">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="F46" t="n">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="G46" t="n">
-        <v>473</v>
+        <v>390</v>
       </c>
       <c r="H46" t="n">
-        <v>455</v>
+        <v>403</v>
       </c>
       <c r="I46" t="n">
-        <v>501</v>
+        <v>392</v>
       </c>
       <c r="J46" t="n">
-        <v>565</v>
+        <v>354</v>
       </c>
       <c r="K46" t="n">
-        <v>499</v>
+        <v>403</v>
       </c>
       <c r="L46" t="n">
-        <v>459.6</v>
+        <v>392.4</v>
       </c>
     </row>
     <row r="47">
@@ -2184,34 +2184,34 @@
         <v>558</v>
       </c>
       <c r="C47" t="n">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D47" t="n">
-        <v>553</v>
+        <v>490</v>
       </c>
       <c r="E47" t="n">
-        <v>564</v>
+        <v>512</v>
       </c>
       <c r="F47" t="n">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="G47" t="n">
-        <v>562</v>
+        <v>490</v>
       </c>
       <c r="H47" t="n">
-        <v>590</v>
+        <v>538</v>
       </c>
       <c r="I47" t="n">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="J47" t="n">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="K47" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L47" t="n">
-        <v>553.1</v>
+        <v>532.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="C48" t="n">
-        <v>652</v>
+        <v>505</v>
       </c>
       <c r="D48" t="n">
-        <v>544</v>
+        <v>505</v>
       </c>
       <c r="E48" t="n">
-        <v>560</v>
+        <v>505</v>
       </c>
       <c r="F48" t="n">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="G48" t="n">
-        <v>611</v>
+        <v>493</v>
       </c>
       <c r="H48" t="n">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="I48" t="n">
-        <v>543</v>
+        <v>592</v>
       </c>
       <c r="J48" t="n">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="K48" t="n">
-        <v>574</v>
+        <v>505</v>
       </c>
       <c r="L48" t="n">
-        <v>564.1</v>
+        <v>517.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>528</v>
+        <v>432</v>
       </c>
       <c r="C49" t="n">
-        <v>500</v>
+        <v>426</v>
       </c>
       <c r="D49" t="n">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="E49" t="n">
-        <v>507</v>
+        <v>412</v>
       </c>
       <c r="F49" t="n">
-        <v>507</v>
+        <v>432</v>
       </c>
       <c r="G49" t="n">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="H49" t="n">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="I49" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="J49" t="n">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="K49" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="L49" t="n">
-        <v>486.1</v>
+        <v>445.9</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>487</v>
+        <v>433</v>
       </c>
       <c r="C50" t="n">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="D50" t="n">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E50" t="n">
+        <v>434</v>
+      </c>
+      <c r="F50" t="n">
+        <v>418</v>
+      </c>
+      <c r="G50" t="n">
         <v>423</v>
       </c>
-      <c r="F50" t="n">
-        <v>524</v>
-      </c>
-      <c r="G50" t="n">
-        <v>524</v>
-      </c>
       <c r="H50" t="n">
-        <v>500</v>
+        <v>459</v>
       </c>
       <c r="I50" t="n">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="J50" t="n">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="K50" t="n">
-        <v>529</v>
+        <v>442</v>
       </c>
       <c r="L50" t="n">
-        <v>476.7</v>
+        <v>430.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C51" t="n">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="D51" t="n">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="E51" t="n">
-        <v>416</v>
+        <v>375</v>
       </c>
       <c r="F51" t="n">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="G51" t="n">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="H51" t="n">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="I51" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="J51" t="n">
-        <v>478</v>
+        <v>430</v>
       </c>
       <c r="K51" t="n">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="L51" t="n">
-        <v>436.4</v>
+        <v>439.3</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>501.54</v>
+        <v>474.88</v>
       </c>
       <c r="C52" t="n">
-        <v>507.98</v>
+        <v>473.36</v>
       </c>
       <c r="D52" t="n">
-        <v>501.18</v>
+        <v>478.52</v>
       </c>
       <c r="E52" t="n">
-        <v>511.38</v>
+        <v>467.48</v>
       </c>
       <c r="F52" t="n">
-        <v>499.98</v>
+        <v>477.1</v>
       </c>
       <c r="G52" t="n">
-        <v>504.48</v>
+        <v>467.36</v>
       </c>
       <c r="H52" t="n">
-        <v>508.12</v>
+        <v>472.48</v>
       </c>
       <c r="I52" t="n">
-        <v>503.62</v>
+        <v>474.82</v>
       </c>
       <c r="J52" t="n">
-        <v>516.3</v>
+        <v>473.86</v>
       </c>
       <c r="K52" t="n">
-        <v>507.64</v>
+        <v>469.88</v>
       </c>
       <c r="L52" t="n">
-        <v>506.222</v>
+        <v>472.974</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.300977468490601</v>
+        <v>2.275913953781128</v>
       </c>
       <c r="C2" t="n">
-        <v>2.276150941848755</v>
+        <v>2.272921562194824</v>
       </c>
       <c r="D2" t="n">
-        <v>2.407758712768555</v>
+        <v>2.156233787536621</v>
       </c>
       <c r="E2" t="n">
-        <v>2.248091220855713</v>
+        <v>2.221060514450073</v>
       </c>
       <c r="F2" t="n">
-        <v>2.27341103553772</v>
+        <v>2.147257804870605</v>
       </c>
       <c r="G2" t="n">
-        <v>2.295374155044556</v>
+        <v>2.133294582366943</v>
       </c>
       <c r="H2" t="n">
-        <v>2.290000200271606</v>
+        <v>2.17318868637085</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18346095085144</v>
+        <v>2.12132716178894</v>
       </c>
       <c r="J2" t="n">
-        <v>2.383910894393921</v>
+        <v>2.207097768783569</v>
       </c>
       <c r="K2" t="n">
-        <v>2.278759002685547</v>
+        <v>2.198122024536133</v>
       </c>
       <c r="L2" t="n">
-        <v>2.293789458274841</v>
+        <v>2.190641784667969</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.377928733825684</v>
+        <v>2.299849510192871</v>
       </c>
       <c r="C3" t="n">
-        <v>2.45990514755249</v>
+        <v>2.521257877349854</v>
       </c>
       <c r="D3" t="n">
-        <v>2.511357069015503</v>
+        <v>2.280900239944458</v>
       </c>
       <c r="E3" t="n">
-        <v>2.68230128288269</v>
+        <v>2.332761764526367</v>
       </c>
       <c r="F3" t="n">
-        <v>2.741368770599365</v>
+        <v>2.371657133102417</v>
       </c>
       <c r="G3" t="n">
-        <v>2.312788724899292</v>
+        <v>2.320793390274048</v>
       </c>
       <c r="H3" t="n">
-        <v>2.21725869178772</v>
+        <v>2.119332551956177</v>
       </c>
       <c r="I3" t="n">
-        <v>2.494984149932861</v>
+        <v>2.245993614196777</v>
       </c>
       <c r="J3" t="n">
-        <v>2.316262483596802</v>
+        <v>2.206100463867188</v>
       </c>
       <c r="K3" t="n">
-        <v>2.394680500030518</v>
+        <v>2.196127414703369</v>
       </c>
       <c r="L3" t="n">
-        <v>2.450883555412292</v>
+        <v>2.289477396011352</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.661843299865723</v>
+        <v>2.358691453933716</v>
       </c>
       <c r="C4" t="n">
-        <v>2.440477132797241</v>
+        <v>2.376643896102905</v>
       </c>
       <c r="D4" t="n">
-        <v>2.348212003707886</v>
+        <v>2.284888982772827</v>
       </c>
       <c r="E4" t="n">
-        <v>2.642083644866943</v>
+        <v>2.645923852920532</v>
       </c>
       <c r="F4" t="n">
-        <v>2.538903474807739</v>
+        <v>2.401577711105347</v>
       </c>
       <c r="G4" t="n">
-        <v>2.542075872421265</v>
+        <v>2.371657848358154</v>
       </c>
       <c r="H4" t="n">
-        <v>2.429047107696533</v>
+        <v>2.446457386016846</v>
       </c>
       <c r="I4" t="n">
-        <v>2.605934381484985</v>
+        <v>2.374649047851562</v>
       </c>
       <c r="J4" t="n">
-        <v>2.430336713790894</v>
+        <v>2.399583101272583</v>
       </c>
       <c r="K4" t="n">
-        <v>2.501790046691895</v>
+        <v>2.349715948104858</v>
       </c>
       <c r="L4" t="n">
-        <v>2.51407036781311</v>
+        <v>2.400978922843933</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.149036645889282</v>
+        <v>2.141273260116577</v>
       </c>
       <c r="C5" t="n">
-        <v>2.311385631561279</v>
+        <v>2.153241872787476</v>
       </c>
       <c r="D5" t="n">
-        <v>2.099236011505127</v>
+        <v>2.12132716178894</v>
       </c>
       <c r="E5" t="n">
-        <v>2.237753629684448</v>
+        <v>2.166207313537598</v>
       </c>
       <c r="F5" t="n">
-        <v>2.145784854888916</v>
+        <v>2.144266128540039</v>
       </c>
       <c r="G5" t="n">
-        <v>2.384235382080078</v>
+        <v>2.145262956619263</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34946346282959</v>
+        <v>2.27790904045105</v>
       </c>
       <c r="I5" t="n">
-        <v>2.413024187088013</v>
+        <v>2.27591347694397</v>
       </c>
       <c r="J5" t="n">
-        <v>2.331873893737793</v>
+        <v>2.093401432037354</v>
       </c>
       <c r="K5" t="n">
-        <v>2.327113151550293</v>
+        <v>2.100382804870605</v>
       </c>
       <c r="L5" t="n">
-        <v>2.274890685081482</v>
+        <v>2.161918544769287</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.12480640411377</v>
+        <v>1.878430366516113</v>
       </c>
       <c r="C6" t="n">
-        <v>2.11618971824646</v>
+        <v>2.174185752868652</v>
       </c>
       <c r="D6" t="n">
-        <v>2.369690179824829</v>
+        <v>1.914878845214844</v>
       </c>
       <c r="E6" t="n">
-        <v>2.29132080078125</v>
+        <v>1.876980781555176</v>
       </c>
       <c r="F6" t="n">
-        <v>2.03047513961792</v>
+        <v>1.895930528640747</v>
       </c>
       <c r="G6" t="n">
-        <v>2.157087564468384</v>
+        <v>1.885955810546875</v>
       </c>
       <c r="H6" t="n">
-        <v>2.063307046890259</v>
+        <v>2.198121786117554</v>
       </c>
       <c r="I6" t="n">
-        <v>2.212716102600098</v>
+        <v>1.928231239318848</v>
       </c>
       <c r="J6" t="n">
-        <v>2.33843207359314</v>
+        <v>2.002644062042236</v>
       </c>
       <c r="K6" t="n">
-        <v>2.007560253143311</v>
+        <v>2.355700492858887</v>
       </c>
       <c r="L6" t="n">
-        <v>2.171158528327942</v>
+        <v>2.011105966567993</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.365036010742188</v>
+        <v>2.5481858253479</v>
       </c>
       <c r="C7" t="n">
-        <v>2.408775806427002</v>
+        <v>2.788542747497559</v>
       </c>
       <c r="D7" t="n">
-        <v>2.360678672790527</v>
+        <v>2.671854496002197</v>
       </c>
       <c r="E7" t="n">
-        <v>2.365052938461304</v>
+        <v>2.269928693771362</v>
       </c>
       <c r="F7" t="n">
-        <v>2.588473558425903</v>
+        <v>2.312815189361572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.384642839431763</v>
+        <v>2.737678289413452</v>
       </c>
       <c r="H7" t="n">
-        <v>2.403766393661499</v>
+        <v>2.447744131088257</v>
       </c>
       <c r="I7" t="n">
-        <v>2.379915475845337</v>
+        <v>2.23103404045105</v>
       </c>
       <c r="J7" t="n">
-        <v>2.447399139404297</v>
+        <v>2.111354112625122</v>
       </c>
       <c r="K7" t="n">
-        <v>2.415195941925049</v>
+        <v>2.192137479782104</v>
       </c>
       <c r="L7" t="n">
-        <v>2.411893677711487</v>
+        <v>2.431127500534058</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.481230497360229</v>
+        <v>2.648005485534668</v>
       </c>
       <c r="C8" t="n">
-        <v>2.661749362945557</v>
+        <v>2.25895881652832</v>
       </c>
       <c r="D8" t="n">
-        <v>2.450221538543701</v>
+        <v>2.261951208114624</v>
       </c>
       <c r="E8" t="n">
-        <v>2.490752696990967</v>
+        <v>2.539968252182007</v>
       </c>
       <c r="F8" t="n">
-        <v>2.703351736068726</v>
+        <v>2.414543628692627</v>
       </c>
       <c r="G8" t="n">
-        <v>2.683127641677856</v>
+        <v>2.53023362159729</v>
       </c>
       <c r="H8" t="n">
-        <v>2.392667055130005</v>
+        <v>2.423521041870117</v>
       </c>
       <c r="I8" t="n">
-        <v>2.476815938949585</v>
+        <v>2.128308296203613</v>
       </c>
       <c r="J8" t="n">
-        <v>2.648923873901367</v>
+        <v>2.368665456771851</v>
       </c>
       <c r="K8" t="n">
-        <v>2.583054304122925</v>
+        <v>2.454436063766479</v>
       </c>
       <c r="L8" t="n">
-        <v>2.557189464569092</v>
+        <v>2.40285918712616</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.385213136672974</v>
+        <v>2.136286735534668</v>
       </c>
       <c r="C9" t="n">
-        <v>2.317024946212769</v>
+        <v>2.221060752868652</v>
       </c>
       <c r="D9" t="n">
-        <v>2.363592863082886</v>
+        <v>2.31181788444519</v>
       </c>
       <c r="E9" t="n">
-        <v>2.386343002319336</v>
+        <v>2.10836124420166</v>
       </c>
       <c r="F9" t="n">
-        <v>2.570261716842651</v>
+        <v>2.07445240020752</v>
       </c>
       <c r="G9" t="n">
-        <v>2.259605407714844</v>
+        <v>2.15024995803833</v>
       </c>
       <c r="H9" t="n">
-        <v>2.242417812347412</v>
+        <v>2.069466114044189</v>
       </c>
       <c r="I9" t="n">
-        <v>2.314002990722656</v>
+        <v>2.145263910293579</v>
       </c>
       <c r="J9" t="n">
-        <v>2.459450483322144</v>
+        <v>2.096393823623657</v>
       </c>
       <c r="K9" t="n">
-        <v>2.336884260177612</v>
+        <v>2.018601894378662</v>
       </c>
       <c r="L9" t="n">
-        <v>2.363479661941528</v>
+        <v>2.133195471763611</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.449542999267578</v>
+        <v>2.086420059204102</v>
       </c>
       <c r="C10" t="n">
-        <v>2.518772602081299</v>
+        <v>2.148255109786987</v>
       </c>
       <c r="D10" t="n">
-        <v>2.472073316574097</v>
+        <v>2.2140793800354</v>
       </c>
       <c r="E10" t="n">
-        <v>2.338121175765991</v>
+        <v>2.040550947189331</v>
       </c>
       <c r="F10" t="n">
-        <v>2.595229148864746</v>
+        <v>2.242710113525391</v>
       </c>
       <c r="G10" t="n">
-        <v>2.325777053833008</v>
+        <v>2.446200370788574</v>
       </c>
       <c r="H10" t="n">
-        <v>2.531466007232666</v>
+        <v>2.268482685089111</v>
       </c>
       <c r="I10" t="n">
-        <v>2.464765787124634</v>
+        <v>2.257973670959473</v>
       </c>
       <c r="J10" t="n">
-        <v>2.396080017089844</v>
+        <v>2.201446056365967</v>
       </c>
       <c r="K10" t="n">
-        <v>2.538176536560059</v>
+        <v>2.064479112625122</v>
       </c>
       <c r="L10" t="n">
-        <v>2.463000464439392</v>
+        <v>2.197059750556946</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>2.081819534301758</v>
+        <v>2.041540384292603</v>
       </c>
       <c r="C11" t="n">
-        <v>2.188605546951294</v>
+        <v>1.818138599395752</v>
       </c>
       <c r="D11" t="n">
-        <v>2.335005044937134</v>
+        <v>1.894931793212891</v>
       </c>
       <c r="E11" t="n">
-        <v>2.12848949432373</v>
+        <v>1.78722071647644</v>
       </c>
       <c r="F11" t="n">
-        <v>2.069282293319702</v>
+        <v>1.829108715057373</v>
       </c>
       <c r="G11" t="n">
-        <v>2.260766506195068</v>
+        <v>1.799188613891602</v>
       </c>
       <c r="H11" t="n">
-        <v>2.164461135864258</v>
+        <v>1.844068050384521</v>
       </c>
       <c r="I11" t="n">
-        <v>2.010029792785645</v>
+        <v>1.896926641464233</v>
       </c>
       <c r="J11" t="n">
-        <v>2.326226472854614</v>
+        <v>1.78721809387207</v>
       </c>
       <c r="K11" t="n">
-        <v>2.143463373184204</v>
+        <v>1.854041576385498</v>
       </c>
       <c r="L11" t="n">
-        <v>2.170814919471741</v>
+        <v>1.855238318443298</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.167012453079224</v>
+        <v>2.019598722457886</v>
       </c>
       <c r="C12" t="n">
-        <v>2.300669193267822</v>
+        <v>2.156234502792358</v>
       </c>
       <c r="D12" t="n">
-        <v>2.530446290969849</v>
+        <v>2.031566858291626</v>
       </c>
       <c r="E12" t="n">
-        <v>2.405240774154663</v>
+        <v>2.050516605377197</v>
       </c>
       <c r="F12" t="n">
-        <v>2.380793333053589</v>
+        <v>2.049518823623657</v>
       </c>
       <c r="G12" t="n">
-        <v>2.356359004974365</v>
+        <v>1.99965238571167</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7010178565979</v>
+        <v>2.045530080795288</v>
       </c>
       <c r="I12" t="n">
-        <v>2.47296929359436</v>
+        <v>2.035555839538574</v>
       </c>
       <c r="J12" t="n">
-        <v>2.383405923843384</v>
+        <v>2.217071533203125</v>
       </c>
       <c r="K12" t="n">
-        <v>2.674148797988892</v>
+        <v>2.034558773040771</v>
       </c>
       <c r="L12" t="n">
-        <v>2.437206292152405</v>
+        <v>2.063980412483216</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.450779914855957</v>
+        <v>2.088414907455444</v>
       </c>
       <c r="C13" t="n">
-        <v>2.36534857749939</v>
+        <v>2.289875984191895</v>
       </c>
       <c r="D13" t="n">
-        <v>2.648797273635864</v>
+        <v>2.157232284545898</v>
       </c>
       <c r="E13" t="n">
-        <v>2.443923711776733</v>
+        <v>2.258958101272583</v>
       </c>
       <c r="F13" t="n">
-        <v>2.468896150588989</v>
+        <v>2.264943599700928</v>
       </c>
       <c r="G13" t="n">
-        <v>2.241583824157715</v>
+        <v>2.285886287689209</v>
       </c>
       <c r="H13" t="n">
-        <v>2.411588191986084</v>
+        <v>2.204106569290161</v>
       </c>
       <c r="I13" t="n">
-        <v>2.623553037643433</v>
+        <v>2.221059799194336</v>
       </c>
       <c r="J13" t="n">
-        <v>2.682998180389404</v>
+        <v>2.138282299041748</v>
       </c>
       <c r="K13" t="n">
-        <v>2.520239114761353</v>
+        <v>2.541204214096069</v>
       </c>
       <c r="L13" t="n">
-        <v>2.485770797729492</v>
+        <v>2.244996404647827</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.453232288360596</v>
+        <v>2.266938447952271</v>
       </c>
       <c r="C14" t="n">
-        <v>2.317352056503296</v>
+        <v>2.28788161277771</v>
       </c>
       <c r="D14" t="n">
-        <v>2.426057815551758</v>
+        <v>2.221060991287231</v>
       </c>
       <c r="E14" t="n">
-        <v>2.332435846328735</v>
+        <v>2.156233310699463</v>
       </c>
       <c r="F14" t="n">
-        <v>2.394136428833008</v>
+        <v>2.255967617034912</v>
       </c>
       <c r="G14" t="n">
-        <v>2.347295761108398</v>
+        <v>2.218067646026611</v>
       </c>
       <c r="H14" t="n">
-        <v>2.721825361251831</v>
+        <v>2.229039192199707</v>
       </c>
       <c r="I14" t="n">
-        <v>2.481597185134888</v>
+        <v>2.221059799194336</v>
       </c>
       <c r="J14" t="n">
-        <v>2.470608234405518</v>
+        <v>2.288879156112671</v>
       </c>
       <c r="K14" t="n">
-        <v>2.600489854812622</v>
+        <v>2.248986482620239</v>
       </c>
       <c r="L14" t="n">
-        <v>2.454503083229065</v>
+        <v>2.239411425590515</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.34260630607605</v>
+        <v>2.031566858291626</v>
       </c>
       <c r="C15" t="n">
-        <v>2.346476793289185</v>
+        <v>2.090382099151611</v>
       </c>
       <c r="D15" t="n">
-        <v>2.257845640182495</v>
+        <v>2.119332313537598</v>
       </c>
       <c r="E15" t="n">
-        <v>2.455911874771118</v>
+        <v>2.092404842376709</v>
       </c>
       <c r="F15" t="n">
-        <v>2.414694547653198</v>
+        <v>2.076246023178101</v>
       </c>
       <c r="G15" t="n">
-        <v>2.415325403213501</v>
+        <v>2.254970073699951</v>
       </c>
       <c r="H15" t="n">
-        <v>2.218631982803345</v>
+        <v>2.335753679275513</v>
       </c>
       <c r="I15" t="n">
-        <v>2.494629144668579</v>
+        <v>2.123322010040283</v>
       </c>
       <c r="J15" t="n">
-        <v>2.378539562225342</v>
+        <v>2.142271280288696</v>
       </c>
       <c r="K15" t="n">
-        <v>2.465160846710205</v>
+        <v>2.160222291946411</v>
       </c>
       <c r="L15" t="n">
-        <v>2.378982210159302</v>
+        <v>2.14264714717865</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.282273292541504</v>
+        <v>2.743662357330322</v>
       </c>
       <c r="C16" t="n">
-        <v>2.594690322875977</v>
+        <v>2.510287046432495</v>
       </c>
       <c r="D16" t="n">
-        <v>2.331146001815796</v>
+        <v>2.366671085357666</v>
       </c>
       <c r="E16" t="n">
-        <v>2.486836433410645</v>
+        <v>2.499176263809204</v>
       </c>
       <c r="F16" t="n">
-        <v>2.425313949584961</v>
+        <v>2.445459604263306</v>
       </c>
       <c r="G16" t="n">
-        <v>2.575592756271362</v>
+        <v>2.372654914855957</v>
       </c>
       <c r="H16" t="n">
-        <v>2.374427080154419</v>
+        <v>2.556164026260376</v>
       </c>
       <c r="I16" t="n">
-        <v>2.384395122528076</v>
+        <v>2.36268162727356</v>
       </c>
       <c r="J16" t="n">
-        <v>2.429828405380249</v>
+        <v>2.30583381652832</v>
       </c>
       <c r="K16" t="n">
-        <v>2.40195369720459</v>
+        <v>2.302841901779175</v>
       </c>
       <c r="L16" t="n">
-        <v>2.428645706176758</v>
+        <v>2.446543264389038</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.325083017349243</v>
+        <v>2.324783563613892</v>
       </c>
       <c r="C17" t="n">
-        <v>2.34184193611145</v>
+        <v>2.101380109786987</v>
       </c>
       <c r="D17" t="n">
-        <v>2.721069097518921</v>
+        <v>2.201114177703857</v>
       </c>
       <c r="E17" t="n">
-        <v>2.268410921096802</v>
+        <v>2.194133043289185</v>
       </c>
       <c r="F17" t="n">
-        <v>2.141561269760132</v>
+        <v>2.227044105529785</v>
       </c>
       <c r="G17" t="n">
-        <v>2.300029039382935</v>
+        <v>2.200116395950317</v>
       </c>
       <c r="H17" t="n">
-        <v>2.345373153686523</v>
+        <v>2.310821056365967</v>
       </c>
       <c r="I17" t="n">
-        <v>2.439094305038452</v>
+        <v>2.184158563613892</v>
       </c>
       <c r="J17" t="n">
-        <v>2.260154962539673</v>
+        <v>2.27691125869751</v>
       </c>
       <c r="K17" t="n">
-        <v>2.300333261489868</v>
+        <v>2.107364416122437</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3442950963974</v>
+        <v>2.212782669067383</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.897566795349121</v>
+        <v>2.462414503097534</v>
       </c>
       <c r="C18" t="n">
-        <v>2.844612836837769</v>
+        <v>2.499315977096558</v>
       </c>
       <c r="D18" t="n">
-        <v>2.551292896270752</v>
+        <v>2.50230860710144</v>
       </c>
       <c r="E18" t="n">
-        <v>2.792081356048584</v>
+        <v>2.48934268951416</v>
       </c>
       <c r="F18" t="n">
-        <v>2.691240072250366</v>
+        <v>2.410553216934204</v>
       </c>
       <c r="G18" t="n">
-        <v>2.631611347198486</v>
+        <v>2.588079690933228</v>
       </c>
       <c r="H18" t="n">
-        <v>2.597748756408691</v>
+        <v>2.461417198181152</v>
       </c>
       <c r="I18" t="n">
-        <v>2.739698886871338</v>
+        <v>2.318812608718872</v>
       </c>
       <c r="J18" t="n">
-        <v>2.618713617324829</v>
+        <v>2.409323692321777</v>
       </c>
       <c r="K18" t="n">
-        <v>2.705134153366089</v>
+        <v>2.6618812084198</v>
       </c>
       <c r="L18" t="n">
-        <v>2.706970071792603</v>
+        <v>2.480344939231872</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.285997629165649</v>
+        <v>2.454437255859375</v>
       </c>
       <c r="C19" t="n">
-        <v>2.310121536254883</v>
+        <v>2.706760883331299</v>
       </c>
       <c r="D19" t="n">
-        <v>2.49004864692688</v>
+        <v>2.442468643188477</v>
       </c>
       <c r="E19" t="n">
-        <v>2.447871685028076</v>
+        <v>3.184484243392944</v>
       </c>
       <c r="F19" t="n">
-        <v>2.48495078086853</v>
+        <v>2.656895160675049</v>
       </c>
       <c r="G19" t="n">
-        <v>2.538513422012329</v>
+        <v>2.36268138885498</v>
       </c>
       <c r="H19" t="n">
-        <v>2.556656122207642</v>
+        <v>2.359689474105835</v>
       </c>
       <c r="I19" t="n">
-        <v>2.550015449523926</v>
+        <v>2.279902696609497</v>
       </c>
       <c r="J19" t="n">
-        <v>2.498024702072144</v>
+        <v>2.295860052108765</v>
       </c>
       <c r="K19" t="n">
-        <v>2.602834701538086</v>
+        <v>3.097715616226196</v>
       </c>
       <c r="L19" t="n">
-        <v>2.476503467559815</v>
+        <v>2.584089541435242</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.563121318817139</v>
+        <v>2.549182653427124</v>
       </c>
       <c r="C20" t="n">
-        <v>2.321336269378662</v>
+        <v>2.277908563613892</v>
       </c>
       <c r="D20" t="n">
-        <v>2.343539476394653</v>
+        <v>2.382627725601196</v>
       </c>
       <c r="E20" t="n">
-        <v>2.196852445602417</v>
+        <v>2.458426475524902</v>
       </c>
       <c r="F20" t="n">
-        <v>2.409846305847168</v>
+        <v>2.379636287689209</v>
       </c>
       <c r="G20" t="n">
-        <v>2.556527137756348</v>
+        <v>2.310820341110229</v>
       </c>
       <c r="H20" t="n">
-        <v>2.372709035873413</v>
+        <v>2.283892869949341</v>
       </c>
       <c r="I20" t="n">
-        <v>2.333571195602417</v>
+        <v>2.500313282012939</v>
       </c>
       <c r="J20" t="n">
-        <v>2.538877010345459</v>
+        <v>2.343732357025146</v>
       </c>
       <c r="K20" t="n">
-        <v>2.178614139556885</v>
+        <v>2.31181788444519</v>
       </c>
       <c r="L20" t="n">
-        <v>2.381499433517456</v>
+        <v>2.379835844039917</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.398658752441406</v>
+        <v>2.395593881607056</v>
       </c>
       <c r="C21" t="n">
-        <v>2.324862003326416</v>
+        <v>2.515274286270142</v>
       </c>
       <c r="D21" t="n">
-        <v>2.252906799316406</v>
+        <v>2.31580662727356</v>
       </c>
       <c r="E21" t="n">
-        <v>2.376684427261353</v>
+        <v>2.500313282012939</v>
       </c>
       <c r="F21" t="n">
-        <v>2.513437747955322</v>
+        <v>2.235022783279419</v>
       </c>
       <c r="G21" t="n">
-        <v>2.294514894485474</v>
+        <v>2.418532609939575</v>
       </c>
       <c r="H21" t="n">
-        <v>2.424506902694702</v>
+        <v>2.385621070861816</v>
       </c>
       <c r="I21" t="n">
-        <v>2.405184984207153</v>
+        <v>2.43748140335083</v>
       </c>
       <c r="J21" t="n">
-        <v>2.277617454528809</v>
+        <v>2.212084054946899</v>
       </c>
       <c r="K21" t="n">
-        <v>2.377971172332764</v>
+        <v>2.406564474105835</v>
       </c>
       <c r="L21" t="n">
-        <v>2.36463451385498</v>
+        <v>2.382229447364807</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.273106575012207</v>
+        <v>2.250980138778687</v>
       </c>
       <c r="C22" t="n">
-        <v>2.225759744644165</v>
+        <v>2.154238939285278</v>
       </c>
       <c r="D22" t="n">
-        <v>2.242076396942139</v>
+        <v>2.236020565032959</v>
       </c>
       <c r="E22" t="n">
-        <v>2.164984226226807</v>
+        <v>2.185156583786011</v>
       </c>
       <c r="F22" t="n">
-        <v>2.557269811630249</v>
+        <v>2.143269062042236</v>
       </c>
       <c r="G22" t="n">
-        <v>2.412797451019287</v>
+        <v>2.300846576690674</v>
       </c>
       <c r="H22" t="n">
-        <v>2.473664283752441</v>
+        <v>2.171194076538086</v>
       </c>
       <c r="I22" t="n">
-        <v>2.316222190856934</v>
+        <v>2.107364177703857</v>
       </c>
       <c r="J22" t="n">
-        <v>2.276193141937256</v>
+        <v>2.161220550537109</v>
       </c>
       <c r="K22" t="n">
-        <v>2.292420387268066</v>
+        <v>2.215076684951782</v>
       </c>
       <c r="L22" t="n">
-        <v>2.323449420928955</v>
+        <v>2.192536735534668</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>2.017947196960449</v>
+        <v>2.08243203163147</v>
       </c>
       <c r="C23" t="n">
-        <v>2.11100172996521</v>
+        <v>1.968734502792358</v>
       </c>
       <c r="D23" t="n">
-        <v>2.018070459365845</v>
+        <v>1.977710962295532</v>
       </c>
       <c r="E23" t="n">
-        <v>2.194559574127197</v>
+        <v>2.030569791793823</v>
       </c>
       <c r="F23" t="n">
-        <v>1.936804294586182</v>
+        <v>2.020596981048584</v>
       </c>
       <c r="G23" t="n">
-        <v>2.040183305740356</v>
+        <v>2.144284725189209</v>
       </c>
       <c r="H23" t="n">
-        <v>1.972845315933228</v>
+        <v>2.096393585205078</v>
       </c>
       <c r="I23" t="n">
-        <v>2.334840774536133</v>
+        <v>2.021593809127808</v>
       </c>
       <c r="J23" t="n">
-        <v>2.076773166656494</v>
+        <v>2.013614892959595</v>
       </c>
       <c r="K23" t="n">
-        <v>1.969436407089233</v>
+        <v>1.981700420379639</v>
       </c>
       <c r="L23" t="n">
-        <v>2.067246222496033</v>
+        <v>2.03376317024231</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>2.350644826889038</v>
+        <v>2.099385499954224</v>
       </c>
       <c r="C24" t="n">
-        <v>2.252704858779907</v>
+        <v>2.048521757125854</v>
       </c>
       <c r="D24" t="n">
-        <v>2.461633443832397</v>
+        <v>2.147258043289185</v>
       </c>
       <c r="E24" t="n">
-        <v>2.268918037414551</v>
+        <v>2.188148021697998</v>
       </c>
       <c r="F24" t="n">
-        <v>2.393871068954468</v>
+        <v>2.113348484039307</v>
       </c>
       <c r="G24" t="n">
-        <v>2.203118801116943</v>
+        <v>2.091407299041748</v>
       </c>
       <c r="H24" t="n">
-        <v>2.249502182006836</v>
+        <v>2.049518823623657</v>
       </c>
       <c r="I24" t="n">
-        <v>2.295023202896118</v>
+        <v>2.028574466705322</v>
       </c>
       <c r="J24" t="n">
-        <v>2.265330791473389</v>
+        <v>1.950782537460327</v>
       </c>
       <c r="K24" t="n">
-        <v>2.124041795730591</v>
+        <v>2.174185991287231</v>
       </c>
       <c r="L24" t="n">
-        <v>2.286478900909424</v>
+        <v>2.089113092422485</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.441850423812866</v>
+        <v>2.2609543800354</v>
       </c>
       <c r="C25" t="n">
-        <v>2.278538227081299</v>
+        <v>2.214078903198242</v>
       </c>
       <c r="D25" t="n">
-        <v>2.247104167938232</v>
+        <v>2.254969596862793</v>
       </c>
       <c r="E25" t="n">
-        <v>2.509124517440796</v>
+        <v>2.335753679275513</v>
       </c>
       <c r="F25" t="n">
-        <v>2.254339456558228</v>
+        <v>2.397587776184082</v>
       </c>
       <c r="G25" t="n">
-        <v>2.208326101303101</v>
+        <v>2.31082010269165</v>
       </c>
       <c r="H25" t="n">
-        <v>2.632267475128174</v>
+        <v>2.243999242782593</v>
       </c>
       <c r="I25" t="n">
-        <v>2.251379013061523</v>
+        <v>2.371658086776733</v>
       </c>
       <c r="J25" t="n">
-        <v>2.406325340270996</v>
+        <v>2.271924734115601</v>
       </c>
       <c r="K25" t="n">
-        <v>2.779975175857544</v>
+        <v>2.290874242782593</v>
       </c>
       <c r="L25" t="n">
-        <v>2.400922989845276</v>
+        <v>2.29526207447052</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.511010408401489</v>
+        <v>2.407561540603638</v>
       </c>
       <c r="C26" t="n">
-        <v>2.449304342269897</v>
+        <v>2.578105688095093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.661572933197021</v>
+        <v>2.337748527526855</v>
       </c>
       <c r="E26" t="n">
-        <v>2.555159091949463</v>
+        <v>2.41454291343689</v>
       </c>
       <c r="F26" t="n">
-        <v>2.90413761138916</v>
+        <v>2.318799257278442</v>
       </c>
       <c r="G26" t="n">
-        <v>2.650045156478882</v>
+        <v>2.357694149017334</v>
       </c>
       <c r="H26" t="n">
-        <v>2.813473224639893</v>
+        <v>2.360687255859375</v>
       </c>
       <c r="I26" t="n">
-        <v>2.45566987991333</v>
+        <v>2.529236316680908</v>
       </c>
       <c r="J26" t="n">
-        <v>2.584959983825684</v>
+        <v>2.361683368682861</v>
       </c>
       <c r="K26" t="n">
-        <v>2.551212549209595</v>
+        <v>2.546191215515137</v>
       </c>
       <c r="L26" t="n">
-        <v>2.613654518127441</v>
+        <v>2.421225023269653</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.565259695053101</v>
+        <v>2.249983310699463</v>
       </c>
       <c r="C27" t="n">
-        <v>2.528409957885742</v>
+        <v>2.13129997253418</v>
       </c>
       <c r="D27" t="n">
-        <v>2.392628908157349</v>
+        <v>2.241006851196289</v>
       </c>
       <c r="E27" t="n">
-        <v>2.267364501953125</v>
+        <v>2.102377653121948</v>
       </c>
       <c r="F27" t="n">
-        <v>2.383815765380859</v>
+        <v>2.150249004364014</v>
       </c>
       <c r="G27" t="n">
-        <v>2.324495315551758</v>
+        <v>2.17717719078064</v>
       </c>
       <c r="H27" t="n">
-        <v>2.272090911865234</v>
+        <v>2.310796737670898</v>
       </c>
       <c r="I27" t="n">
-        <v>2.404240131378174</v>
+        <v>2.287881851196289</v>
       </c>
       <c r="J27" t="n">
-        <v>2.394983053207397</v>
+        <v>2.281898260116577</v>
       </c>
       <c r="K27" t="n">
-        <v>2.232832670211792</v>
+        <v>2.220062494277954</v>
       </c>
       <c r="L27" t="n">
-        <v>2.376612091064453</v>
+        <v>2.215273332595825</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.224450588226318</v>
+        <v>2.325780153274536</v>
       </c>
       <c r="C28" t="n">
-        <v>2.138832330703735</v>
+        <v>2.282895088195801</v>
       </c>
       <c r="D28" t="n">
-        <v>2.137348890304565</v>
+        <v>2.289876222610474</v>
       </c>
       <c r="E28" t="n">
-        <v>2.411177396774292</v>
+        <v>2.396591186523438</v>
       </c>
       <c r="F28" t="n">
-        <v>2.358695030212402</v>
+        <v>2.20111346244812</v>
       </c>
       <c r="G28" t="n">
-        <v>2.249835014343262</v>
+        <v>2.314809799194336</v>
       </c>
       <c r="H28" t="n">
-        <v>2.197015762329102</v>
+        <v>2.255967378616333</v>
       </c>
       <c r="I28" t="n">
-        <v>2.183332681655884</v>
+        <v>2.329769611358643</v>
       </c>
       <c r="J28" t="n">
-        <v>2.268445491790771</v>
+        <v>2.264943599700928</v>
       </c>
       <c r="K28" t="n">
-        <v>2.082249641418457</v>
+        <v>2.260953664779663</v>
       </c>
       <c r="L28" t="n">
-        <v>2.225138282775879</v>
+        <v>2.292270016670227</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.167406320571899</v>
+        <v>2.216073513031006</v>
       </c>
       <c r="C29" t="n">
-        <v>2.303059816360474</v>
+        <v>2.37564754486084</v>
       </c>
       <c r="D29" t="n">
-        <v>2.460026979446411</v>
+        <v>2.125316619873047</v>
       </c>
       <c r="E29" t="n">
-        <v>2.219910860061646</v>
+        <v>2.003641605377197</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2923264503479</v>
+        <v>2.032564640045166</v>
       </c>
       <c r="G29" t="n">
-        <v>2.21448016166687</v>
+        <v>2.111353635787964</v>
       </c>
       <c r="H29" t="n">
-        <v>2.198152542114258</v>
+        <v>2.19612717628479</v>
       </c>
       <c r="I29" t="n">
-        <v>2.430212259292603</v>
+        <v>1.92186164855957</v>
       </c>
       <c r="J29" t="n">
-        <v>2.272768974304199</v>
+        <v>2.033561944961548</v>
       </c>
       <c r="K29" t="n">
-        <v>2.303086519241333</v>
+        <v>2.046527147293091</v>
       </c>
       <c r="L29" t="n">
-        <v>2.286143088340759</v>
+        <v>2.106267547607422</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.293744564056396</v>
+        <v>2.165209293365479</v>
       </c>
       <c r="C30" t="n">
-        <v>2.375386714935303</v>
+        <v>2.119332551956177</v>
       </c>
       <c r="D30" t="n">
-        <v>2.457080364227295</v>
+        <v>2.30583381652832</v>
       </c>
       <c r="E30" t="n">
-        <v>2.359700679779053</v>
+        <v>2.064479112625122</v>
       </c>
       <c r="F30" t="n">
-        <v>2.148019790649414</v>
+        <v>2.176180362701416</v>
       </c>
       <c r="G30" t="n">
-        <v>2.161742925643921</v>
+        <v>2.139278888702393</v>
       </c>
       <c r="H30" t="n">
-        <v>2.407885551452637</v>
+        <v>2.193135023117065</v>
       </c>
       <c r="I30" t="n">
-        <v>2.410962343215942</v>
+        <v>2.234025478363037</v>
       </c>
       <c r="J30" t="n">
-        <v>2.473080396652222</v>
+        <v>1.98868203163147</v>
       </c>
       <c r="K30" t="n">
-        <v>2.508378267288208</v>
+        <v>2.083428621292114</v>
       </c>
       <c r="L30" t="n">
-        <v>2.359598159790039</v>
+        <v>2.146958518028259</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>2.102890014648438</v>
+        <v>1.799187898635864</v>
       </c>
       <c r="C31" t="n">
-        <v>2.294081449508667</v>
+        <v>1.868004560470581</v>
       </c>
       <c r="D31" t="n">
-        <v>2.038116693496704</v>
+        <v>1.766277551651001</v>
       </c>
       <c r="E31" t="n">
-        <v>2.040834903717041</v>
+        <v>1.852047204971313</v>
       </c>
       <c r="F31" t="n">
-        <v>1.951433420181274</v>
+        <v>1.786223173141479</v>
       </c>
       <c r="G31" t="n">
-        <v>2.04009222984314</v>
+        <v>1.87398886680603</v>
       </c>
       <c r="H31" t="n">
-        <v>2.178479671478271</v>
+        <v>1.863018274307251</v>
       </c>
       <c r="I31" t="n">
-        <v>1.943495750427246</v>
+        <v>1.780239105224609</v>
       </c>
       <c r="J31" t="n">
-        <v>2.001215934753418</v>
+        <v>1.890942573547363</v>
       </c>
       <c r="K31" t="n">
-        <v>2.026269674301147</v>
+        <v>1.79220724105835</v>
       </c>
       <c r="L31" t="n">
-        <v>2.061690974235534</v>
+        <v>1.827213644981384</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.366650104522705</v>
+        <v>1.949786424636841</v>
       </c>
       <c r="C32" t="n">
-        <v>2.450483322143555</v>
+        <v>1.957763195037842</v>
       </c>
       <c r="D32" t="n">
-        <v>2.253755569458008</v>
+        <v>1.906900405883789</v>
       </c>
       <c r="E32" t="n">
-        <v>2.164701700210571</v>
+        <v>1.878974676132202</v>
       </c>
       <c r="F32" t="n">
-        <v>2.331475257873535</v>
+        <v>1.963748455047607</v>
       </c>
       <c r="G32" t="n">
-        <v>2.840346097946167</v>
+        <v>1.961754083633423</v>
       </c>
       <c r="H32" t="n">
-        <v>2.145336151123047</v>
+        <v>2.157231330871582</v>
       </c>
       <c r="I32" t="n">
-        <v>2.193508386611938</v>
+        <v>1.882964134216309</v>
       </c>
       <c r="J32" t="n">
-        <v>2.278100728988647</v>
+        <v>1.883961915969849</v>
       </c>
       <c r="K32" t="n">
-        <v>2.183719635009766</v>
+        <v>1.947261571884155</v>
       </c>
       <c r="L32" t="n">
-        <v>2.320807695388794</v>
+        <v>1.94903461933136</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.145925998687744</v>
+        <v>1.979705333709717</v>
       </c>
       <c r="C33" t="n">
-        <v>2.585958242416382</v>
+        <v>2.224052429199219</v>
       </c>
       <c r="D33" t="n">
-        <v>2.297711849212646</v>
+        <v>2.048522710800171</v>
       </c>
       <c r="E33" t="n">
-        <v>2.41395092010498</v>
+        <v>2.121326446533203</v>
       </c>
       <c r="F33" t="n">
-        <v>2.260841608047485</v>
+        <v>1.979706048965454</v>
       </c>
       <c r="G33" t="n">
-        <v>2.264659881591797</v>
+        <v>2.157231330871582</v>
       </c>
       <c r="H33" t="n">
-        <v>2.573245286941528</v>
+        <v>2.071460723876953</v>
       </c>
       <c r="I33" t="n">
-        <v>2.276978254318237</v>
+        <v>2.068468570709229</v>
       </c>
       <c r="J33" t="n">
-        <v>2.267170429229736</v>
+        <v>1.940809965133667</v>
       </c>
       <c r="K33" t="n">
-        <v>2.242187976837158</v>
+        <v>2.061487674713135</v>
       </c>
       <c r="L33" t="n">
-        <v>2.33286304473877</v>
+        <v>2.065277123451233</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>2.169529676437378</v>
+        <v>1.795199155807495</v>
       </c>
       <c r="C34" t="n">
-        <v>2.280526399612427</v>
+        <v>1.967737674713135</v>
       </c>
       <c r="D34" t="n">
-        <v>2.106496334075928</v>
+        <v>1.921860933303833</v>
       </c>
       <c r="E34" t="n">
-        <v>2.110170602798462</v>
+        <v>2.002354383468628</v>
       </c>
       <c r="F34" t="n">
-        <v>2.10557746887207</v>
+        <v>1.921860456466675</v>
       </c>
       <c r="G34" t="n">
-        <v>2.244374752044678</v>
+        <v>2.256965160369873</v>
       </c>
       <c r="H34" t="n">
-        <v>1.893213748931885</v>
+        <v>2.218068599700928</v>
       </c>
       <c r="I34" t="n">
-        <v>2.169668674468994</v>
+        <v>2.561165571212769</v>
       </c>
       <c r="J34" t="n">
-        <v>2.086525678634644</v>
+        <v>2.471392869949341</v>
       </c>
       <c r="K34" t="n">
-        <v>1.993883848190308</v>
+        <v>2.525246858596802</v>
       </c>
       <c r="L34" t="n">
-        <v>2.115996718406677</v>
+        <v>2.164185166358948</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.561895370483398</v>
+        <v>3.154563426971436</v>
       </c>
       <c r="C35" t="n">
-        <v>2.646666288375854</v>
+        <v>2.769593477249146</v>
       </c>
       <c r="D35" t="n">
-        <v>2.490311861038208</v>
+        <v>2.847386360168457</v>
       </c>
       <c r="E35" t="n">
-        <v>2.759734153747559</v>
+        <v>2.917198419570923</v>
       </c>
       <c r="F35" t="n">
-        <v>2.456366539001465</v>
+        <v>2.645924091339111</v>
       </c>
       <c r="G35" t="n">
-        <v>2.759429454803467</v>
+        <v>2.580099821090698</v>
       </c>
       <c r="H35" t="n">
-        <v>2.459351539611816</v>
+        <v>3.597379684448242</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5169358253479</v>
+        <v>3.061812162399292</v>
       </c>
       <c r="J35" t="n">
-        <v>2.62687611579895</v>
+        <v>2.596057653427124</v>
       </c>
       <c r="K35" t="n">
-        <v>2.833207607269287</v>
+        <v>2.758623600006104</v>
       </c>
       <c r="L35" t="n">
-        <v>2.61107747554779</v>
+        <v>2.892863869667053</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>2.060312986373901</v>
+        <v>2.041540145874023</v>
       </c>
       <c r="C36" t="n">
-        <v>2.257628679275513</v>
+        <v>2.103390216827393</v>
       </c>
       <c r="D36" t="n">
-        <v>2.191522598266602</v>
+        <v>2.228041172027588</v>
       </c>
       <c r="E36" t="n">
-        <v>2.161443948745728</v>
+        <v>2.387616634368896</v>
       </c>
       <c r="F36" t="n">
-        <v>3.775252342224121</v>
+        <v>2.73668098449707</v>
       </c>
       <c r="G36" t="n">
-        <v>2.017741918563843</v>
+        <v>2.091407537460327</v>
       </c>
       <c r="H36" t="n">
-        <v>2.17354941368103</v>
+        <v>2.40955638885498</v>
       </c>
       <c r="I36" t="n">
-        <v>2.062164306640625</v>
+        <v>2.179172039031982</v>
       </c>
       <c r="J36" t="n">
-        <v>2.104457139968872</v>
+        <v>2.170197486877441</v>
       </c>
       <c r="K36" t="n">
-        <v>2.061114072799683</v>
+        <v>2.030568838119507</v>
       </c>
       <c r="L36" t="n">
-        <v>2.286518740653992</v>
+        <v>2.237817144393921</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.263149261474609</v>
+        <v>2.308825492858887</v>
       </c>
       <c r="C37" t="n">
-        <v>2.202955961227417</v>
+        <v>2.276910781860352</v>
       </c>
       <c r="D37" t="n">
-        <v>2.342567920684814</v>
+        <v>2.410552978515625</v>
       </c>
       <c r="E37" t="n">
-        <v>2.488367319107056</v>
+        <v>2.139972925186157</v>
       </c>
       <c r="F37" t="n">
-        <v>2.350231647491455</v>
+        <v>2.48535418510437</v>
       </c>
       <c r="G37" t="n">
-        <v>2.494869947433472</v>
+        <v>2.361564874649048</v>
       </c>
       <c r="H37" t="n">
-        <v>2.527021169662476</v>
+        <v>2.642932653427124</v>
       </c>
       <c r="I37" t="n">
-        <v>2.631505250930786</v>
+        <v>2.344729661941528</v>
       </c>
       <c r="J37" t="n">
-        <v>2.386359453201294</v>
+        <v>2.49133825302124</v>
       </c>
       <c r="K37" t="n">
-        <v>2.432246923446655</v>
+        <v>2.28588604927063</v>
       </c>
       <c r="L37" t="n">
-        <v>2.411927485466003</v>
+        <v>2.374806785583496</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.680788040161133</v>
+        <v>2.463412523269653</v>
       </c>
       <c r="C38" t="n">
-        <v>2.924068927764893</v>
+        <v>2.425513505935669</v>
       </c>
       <c r="D38" t="n">
-        <v>2.77412748336792</v>
+        <v>2.638942718505859</v>
       </c>
       <c r="E38" t="n">
-        <v>2.55964207649231</v>
+        <v>2.378639221191406</v>
       </c>
       <c r="F38" t="n">
-        <v>2.660546064376831</v>
+        <v>2.577108144760132</v>
       </c>
       <c r="G38" t="n">
-        <v>2.894287109375</v>
+        <v>2.457428932189941</v>
       </c>
       <c r="H38" t="n">
-        <v>2.827868700027466</v>
+        <v>2.34572696685791</v>
       </c>
       <c r="I38" t="n">
-        <v>2.653581857681274</v>
+        <v>2.470393180847168</v>
       </c>
       <c r="J38" t="n">
-        <v>2.669309377670288</v>
+        <v>2.490339517593384</v>
       </c>
       <c r="K38" t="n">
-        <v>2.64695405960083</v>
+        <v>2.648916482925415</v>
       </c>
       <c r="L38" t="n">
-        <v>2.729117369651795</v>
+        <v>2.489642119407654</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.230638027191162</v>
+        <v>2.116340398788452</v>
       </c>
       <c r="C39" t="n">
-        <v>2.256137847900391</v>
+        <v>2.416538000106812</v>
       </c>
       <c r="D39" t="n">
-        <v>2.320006608963013</v>
+        <v>2.2808997631073</v>
       </c>
       <c r="E39" t="n">
-        <v>2.427935123443604</v>
+        <v>2.254970073699951</v>
       </c>
       <c r="F39" t="n">
-        <v>2.174680709838867</v>
+        <v>2.137284517288208</v>
       </c>
       <c r="G39" t="n">
-        <v>2.158770561218262</v>
+        <v>2.273919105529785</v>
       </c>
       <c r="H39" t="n">
-        <v>2.208934783935547</v>
+        <v>2.225049734115601</v>
       </c>
       <c r="I39" t="n">
-        <v>2.457598447799683</v>
+        <v>4.006287097930908</v>
       </c>
       <c r="J39" t="n">
-        <v>2.269839286804199</v>
+        <v>2.119331836700439</v>
       </c>
       <c r="K39" t="n">
-        <v>2.279542922973633</v>
+        <v>2.256239891052246</v>
       </c>
       <c r="L39" t="n">
-        <v>2.278408432006836</v>
+        <v>2.40868604183197</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.29872727394104</v>
+        <v>2.136288166046143</v>
       </c>
       <c r="C40" t="n">
-        <v>2.219794988632202</v>
+        <v>2.299850225448608</v>
       </c>
       <c r="D40" t="n">
-        <v>2.250449419021606</v>
+        <v>2.252975463867188</v>
       </c>
       <c r="E40" t="n">
-        <v>2.306461334228516</v>
+        <v>2.156233549118042</v>
       </c>
       <c r="F40" t="n">
-        <v>2.139005661010742</v>
+        <v>2.181922197341919</v>
       </c>
       <c r="G40" t="n">
-        <v>2.210188865661621</v>
+        <v>2.170718908309937</v>
       </c>
       <c r="H40" t="n">
-        <v>2.278075456619263</v>
+        <v>2.21806788444519</v>
       </c>
       <c r="I40" t="n">
-        <v>2.089187383651733</v>
+        <v>2.176031589508057</v>
       </c>
       <c r="J40" t="n">
-        <v>2.269697189331055</v>
+        <v>2.163215160369873</v>
       </c>
       <c r="K40" t="n">
-        <v>2.383116960525513</v>
+        <v>2.831427574157715</v>
       </c>
       <c r="L40" t="n">
-        <v>2.244470453262329</v>
+        <v>2.258673071861267</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.347760677337646</v>
+        <v>2.613012552261353</v>
       </c>
       <c r="C41" t="n">
-        <v>2.670974969863892</v>
+        <v>2.598052263259888</v>
       </c>
       <c r="D41" t="n">
-        <v>2.416970014572144</v>
+        <v>2.447454452514648</v>
       </c>
       <c r="E41" t="n">
-        <v>2.425993680953979</v>
+        <v>2.591071128845215</v>
       </c>
       <c r="F41" t="n">
-        <v>2.769115447998047</v>
+        <v>2.460420846939087</v>
       </c>
       <c r="G41" t="n">
-        <v>2.784128665924072</v>
+        <v>2.612014770507812</v>
       </c>
       <c r="H41" t="n">
-        <v>2.65412974357605</v>
+        <v>2.246991157531738</v>
       </c>
       <c r="I41" t="n">
-        <v>2.414688110351562</v>
+        <v>3.044857501983643</v>
       </c>
       <c r="J41" t="n">
-        <v>2.51086950302124</v>
+        <v>2.578105926513672</v>
       </c>
       <c r="K41" t="n">
-        <v>2.566515922546387</v>
+        <v>2.496325016021729</v>
       </c>
       <c r="L41" t="n">
-        <v>2.556114673614502</v>
+        <v>2.568830561637879</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>2.082801342010498</v>
+        <v>2.030568599700928</v>
       </c>
       <c r="C42" t="n">
-        <v>2.220939874649048</v>
+        <v>2.336750030517578</v>
       </c>
       <c r="D42" t="n">
-        <v>2.325155973434448</v>
+        <v>2.016606330871582</v>
       </c>
       <c r="E42" t="n">
-        <v>2.219997882843018</v>
+        <v>2.332761526107788</v>
       </c>
       <c r="F42" t="n">
-        <v>2.280275583267212</v>
+        <v>2.288878440856934</v>
       </c>
       <c r="G42" t="n">
-        <v>2.122660875320435</v>
+        <v>2.152244567871094</v>
       </c>
       <c r="H42" t="n">
-        <v>2.007275104522705</v>
+        <v>2.273918390274048</v>
       </c>
       <c r="I42" t="n">
-        <v>2.290125370025635</v>
+        <v>2.403573036193848</v>
       </c>
       <c r="J42" t="n">
-        <v>2.083575963973999</v>
+        <v>2.368664741516113</v>
       </c>
       <c r="K42" t="n">
-        <v>2.442930221557617</v>
+        <v>2.126314401626587</v>
       </c>
       <c r="L42" t="n">
-        <v>2.207573819160461</v>
+        <v>2.23302800655365</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.325145721435547</v>
+        <v>2.528238534927368</v>
       </c>
       <c r="C43" t="n">
-        <v>2.584730386734009</v>
+        <v>2.395593643188477</v>
       </c>
       <c r="D43" t="n">
-        <v>2.420794725418091</v>
+        <v>2.594062566757202</v>
       </c>
       <c r="E43" t="n">
-        <v>2.216276407241821</v>
+        <v>2.356698513031006</v>
       </c>
       <c r="F43" t="n">
-        <v>2.507728099822998</v>
+        <v>2.526243925094604</v>
       </c>
       <c r="G43" t="n">
-        <v>2.347666263580322</v>
+        <v>2.832426071166992</v>
       </c>
       <c r="H43" t="n">
-        <v>2.467829704284668</v>
+        <v>2.486350059509277</v>
       </c>
       <c r="I43" t="n">
-        <v>2.294406414031982</v>
+        <v>2.280901432037354</v>
       </c>
       <c r="J43" t="n">
-        <v>2.200016736984253</v>
+        <v>2.611018180847168</v>
       </c>
       <c r="K43" t="n">
-        <v>2.323026657104492</v>
+        <v>2.41454291343689</v>
       </c>
       <c r="L43" t="n">
-        <v>2.368762111663818</v>
+        <v>2.502607583999634</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.231070280075073</v>
+        <v>2.262947559356689</v>
       </c>
       <c r="C44" t="n">
-        <v>2.378615140914917</v>
+        <v>2.016607522964478</v>
       </c>
       <c r="D44" t="n">
-        <v>2.138040781021118</v>
+        <v>2.215311050415039</v>
       </c>
       <c r="E44" t="n">
-        <v>2.333310842514038</v>
+        <v>2.205102443695068</v>
       </c>
       <c r="F44" t="n">
-        <v>2.23029613494873</v>
+        <v>2.332761764526367</v>
       </c>
       <c r="G44" t="n">
-        <v>2.34868311882019</v>
+        <v>2.16920018196106</v>
       </c>
       <c r="H44" t="n">
-        <v>2.159730672836304</v>
+        <v>2.326777219772339</v>
       </c>
       <c r="I44" t="n">
-        <v>2.422582149505615</v>
+        <v>2.088415145874023</v>
       </c>
       <c r="J44" t="n">
-        <v>2.216622352600098</v>
+        <v>2.239012956619263</v>
       </c>
       <c r="K44" t="n">
-        <v>2.263957738876343</v>
+        <v>2.22819447517395</v>
       </c>
       <c r="L44" t="n">
-        <v>2.272290921211243</v>
+        <v>2.208433032035828</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.311030149459839</v>
+        <v>2.313811779022217</v>
       </c>
       <c r="C45" t="n">
-        <v>1.99003005027771</v>
+        <v>1.981701612472534</v>
       </c>
       <c r="D45" t="n">
-        <v>2.346977710723877</v>
+        <v>2.451376438140869</v>
       </c>
       <c r="E45" t="n">
-        <v>2.280041217803955</v>
+        <v>2.178174495697021</v>
       </c>
       <c r="F45" t="n">
-        <v>2.027429103851318</v>
+        <v>2.235023498535156</v>
       </c>
       <c r="G45" t="n">
-        <v>2.160737037658691</v>
+        <v>2.089411973953247</v>
       </c>
       <c r="H45" t="n">
-        <v>2.149186611175537</v>
+        <v>2.060489416122437</v>
       </c>
       <c r="I45" t="n">
-        <v>2.229084730148315</v>
+        <v>2.214079618453979</v>
       </c>
       <c r="J45" t="n">
-        <v>2.081716775894165</v>
+        <v>2.334754943847656</v>
       </c>
       <c r="K45" t="n">
-        <v>2.227744340896606</v>
+        <v>2.262947559356689</v>
       </c>
       <c r="L45" t="n">
-        <v>2.180397772789001</v>
+        <v>2.212177133560181</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>2.017853260040283</v>
+        <v>2.062484979629517</v>
       </c>
       <c r="C46" t="n">
-        <v>1.9692702293396</v>
+        <v>2.407561302185059</v>
       </c>
       <c r="D46" t="n">
-        <v>2.059622764587402</v>
+        <v>1.880969524383545</v>
       </c>
       <c r="E46" t="n">
-        <v>2.218574047088623</v>
+        <v>1.976713895797729</v>
       </c>
       <c r="F46" t="n">
-        <v>1.94047737121582</v>
+        <v>2.138281583786011</v>
       </c>
       <c r="G46" t="n">
-        <v>2.12770938873291</v>
+        <v>1.899237871170044</v>
       </c>
       <c r="H46" t="n">
-        <v>2.111897945404053</v>
+        <v>2.117351770401001</v>
       </c>
       <c r="I46" t="n">
-        <v>2.232120752334595</v>
+        <v>2.037551403045654</v>
       </c>
       <c r="J46" t="n">
-        <v>2.091190099716187</v>
+        <v>1.989679336547852</v>
       </c>
       <c r="K46" t="n">
-        <v>2.050026178359985</v>
+        <v>2.695790767669678</v>
       </c>
       <c r="L46" t="n">
-        <v>2.081874203681946</v>
+        <v>2.120562243461609</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.746583938598633</v>
+        <v>2.846387624740601</v>
       </c>
       <c r="C47" t="n">
-        <v>2.701622486114502</v>
+        <v>2.874650955200195</v>
       </c>
       <c r="D47" t="n">
-        <v>2.604799270629883</v>
+        <v>2.595060348510742</v>
       </c>
       <c r="E47" t="n">
-        <v>2.778614282608032</v>
+        <v>2.67484712600708</v>
       </c>
       <c r="F47" t="n">
-        <v>2.860312938690186</v>
+        <v>2.637964487075806</v>
       </c>
       <c r="G47" t="n">
-        <v>2.831402540206909</v>
+        <v>2.735684633255005</v>
       </c>
       <c r="H47" t="n">
-        <v>2.947952747344971</v>
+        <v>2.64534854888916</v>
       </c>
       <c r="I47" t="n">
-        <v>2.623516321182251</v>
+        <v>2.74366307258606</v>
       </c>
       <c r="J47" t="n">
-        <v>2.891399383544922</v>
+        <v>2.96806263923645</v>
       </c>
       <c r="K47" t="n">
-        <v>2.883152008056641</v>
+        <v>2.80749249458313</v>
       </c>
       <c r="L47" t="n">
-        <v>2.786935591697693</v>
+        <v>2.752916193008423</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.483572006225586</v>
+        <v>2.736682176589966</v>
       </c>
       <c r="C48" t="n">
-        <v>2.578979730606079</v>
+        <v>2.579102993011475</v>
       </c>
       <c r="D48" t="n">
-        <v>2.344114065170288</v>
+        <v>2.302842140197754</v>
       </c>
       <c r="E48" t="n">
-        <v>2.235928058624268</v>
+        <v>2.320704221725464</v>
       </c>
       <c r="F48" t="n">
-        <v>2.320767164230347</v>
+        <v>2.31181788444519</v>
       </c>
       <c r="G48" t="n">
-        <v>2.44160008430481</v>
+        <v>2.427507400512695</v>
       </c>
       <c r="H48" t="n">
-        <v>2.187713146209717</v>
+        <v>2.315806865692139</v>
       </c>
       <c r="I48" t="n">
-        <v>2.504968404769897</v>
+        <v>2.391603946685791</v>
       </c>
       <c r="J48" t="n">
-        <v>2.632953643798828</v>
+        <v>2.472388029098511</v>
       </c>
       <c r="K48" t="n">
-        <v>2.334214448928833</v>
+        <v>2.555166482925415</v>
       </c>
       <c r="L48" t="n">
-        <v>2.406481075286865</v>
+        <v>2.44136221408844</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.719375848770142</v>
+        <v>2.535220861434937</v>
       </c>
       <c r="C49" t="n">
-        <v>2.451997518539429</v>
+        <v>2.461417675018311</v>
       </c>
       <c r="D49" t="n">
-        <v>2.425175905227661</v>
+        <v>2.670857429504395</v>
       </c>
       <c r="E49" t="n">
-        <v>2.575871467590332</v>
+        <v>2.328771829605103</v>
       </c>
       <c r="F49" t="n">
-        <v>2.451423406600952</v>
+        <v>2.315807104110718</v>
       </c>
       <c r="G49" t="n">
-        <v>2.735556364059448</v>
+        <v>2.274916648864746</v>
       </c>
       <c r="H49" t="n">
-        <v>2.407914876937866</v>
+        <v>2.462507963180542</v>
       </c>
       <c r="I49" t="n">
-        <v>2.677159786224365</v>
+        <v>2.420527219772339</v>
       </c>
       <c r="J49" t="n">
-        <v>2.53669285774231</v>
+        <v>3.162542104721069</v>
       </c>
       <c r="K49" t="n">
-        <v>2.473203897476196</v>
+        <v>2.786547183990479</v>
       </c>
       <c r="L49" t="n">
-        <v>2.54543719291687</v>
+        <v>2.541911602020264</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.274619579315186</v>
+        <v>2.706760883331299</v>
       </c>
       <c r="C50" t="n">
-        <v>2.190932750701904</v>
+        <v>2.333759546279907</v>
       </c>
       <c r="D50" t="n">
-        <v>2.734636306762695</v>
+        <v>2.730697393417358</v>
       </c>
       <c r="E50" t="n">
-        <v>2.888393402099609</v>
+        <v>2.374649286270142</v>
       </c>
       <c r="F50" t="n">
-        <v>2.655392169952393</v>
+        <v>2.737679004669189</v>
       </c>
       <c r="G50" t="n">
-        <v>2.16229248046875</v>
+        <v>2.282895803451538</v>
       </c>
       <c r="H50" t="n">
-        <v>2.429261684417725</v>
+        <v>2.371664762496948</v>
       </c>
       <c r="I50" t="n">
-        <v>2.021250009536743</v>
+        <v>2.208096027374268</v>
       </c>
       <c r="J50" t="n">
-        <v>3.327447891235352</v>
+        <v>2.439477205276489</v>
       </c>
       <c r="K50" t="n">
-        <v>2.369244337081909</v>
+        <v>2.473387479782104</v>
       </c>
       <c r="L50" t="n">
-        <v>2.505347061157226</v>
+        <v>2.465906739234924</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1.996061325073242</v>
+        <v>2.242004632949829</v>
       </c>
       <c r="C51" t="n">
-        <v>2.17483115196228</v>
+        <v>1.933828830718994</v>
       </c>
       <c r="D51" t="n">
-        <v>2.043633699417114</v>
+        <v>2.15523624420166</v>
       </c>
       <c r="E51" t="n">
-        <v>2.042474269866943</v>
+        <v>2.160222053527832</v>
       </c>
       <c r="F51" t="n">
-        <v>2.01685619354248</v>
+        <v>1.995663404464722</v>
       </c>
       <c r="G51" t="n">
-        <v>2.140871047973633</v>
+        <v>2.170197010040283</v>
       </c>
       <c r="H51" t="n">
-        <v>2.012079238891602</v>
+        <v>1.861023664474487</v>
       </c>
       <c r="I51" t="n">
-        <v>1.970659494400024</v>
+        <v>2.15523624420166</v>
       </c>
       <c r="J51" t="n">
-        <v>2.047593832015991</v>
+        <v>2.309822797775269</v>
       </c>
       <c r="K51" t="n">
-        <v>2.167803049087524</v>
+        <v>2.155237674713135</v>
       </c>
       <c r="L51" t="n">
-        <v>2.061286330223083</v>
+        <v>2.113847255706787</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.336111359596253</v>
+        <v>2.28865038394928</v>
       </c>
       <c r="C52" t="n">
-        <v>2.369211449623108</v>
+        <v>2.285394868850708</v>
       </c>
       <c r="D52" t="n">
-        <v>2.365470108985901</v>
+        <v>2.262632565498352</v>
       </c>
       <c r="E52" t="n">
-        <v>2.372323517799377</v>
+        <v>2.263665270805359</v>
       </c>
       <c r="F52" t="n">
-        <v>2.401523518562317</v>
+        <v>2.255713396072388</v>
       </c>
       <c r="G52" t="n">
-        <v>2.36911853313446</v>
+        <v>2.266209301948547</v>
       </c>
       <c r="H52" t="n">
-        <v>2.356505680084228</v>
+        <v>2.284697360992431</v>
       </c>
       <c r="I52" t="n">
-        <v>2.364748530387879</v>
+        <v>2.292834038734436</v>
       </c>
       <c r="J52" t="n">
-        <v>2.38432309627533</v>
+        <v>2.26247163772583</v>
       </c>
       <c r="K52" t="n">
-        <v>2.367625060081482</v>
+        <v>2.312314295768738</v>
       </c>
       <c r="L52" t="n">
-        <v>2.368696085453033</v>
+        <v>2.277458312034607</v>
       </c>
     </row>
   </sheetData>
